--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0073.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0073.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Starblind Crashsite</t>
+          <t>Bãi Đổ Nát Starblind</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Mount Gjallar</t>
+          <t>Thú cưỡi Gjallar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Upphaf Forest Ruins</t>
+          <t>Tàn Tích Rừng Upphaf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Frostlands Transit Port</t>
+          <t>Trạm Trung Chuyển Vùng Đất Băng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Roya Frostlands: Frostlands Surface</t>
+          <t>Vùng Đất Băng Giá Roya: Bề Mặt Lãnh Nguyên</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Tidelost Forest</t>
+          <t>Rừng Thủy Triều Lạc Lối</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Starblind Crashsite</t>
+          <t>Bãi Đổ Nát Starblind</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mount Gjallar</t>
+          <t>Thú cưỡi Gjallar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Upphaf Forest Ruins</t>
+          <t>Tàn Tích Rừng Upphaf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Frostlands Transit Port</t>
+          <t>Trạm Trung Chuyển Vùng Đất Băng</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Nơi Các Vì Sao Rơi Xuống</t>
+          <t>Nơi Sao Rơi Như Mưa</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dấu chân trên Frostlands</t>
+          <t>Dấu chân trên vùng đất băng giá</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Implementation</t>
+          <t>Chiến Dịch Lollo: Thực Thi</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Món Quà Từ Tuyết Mềm</t>
+          <t>Quà tặng của Tuyết Mềm</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Mạch Đất Của Vùng Băng Giá</t>
+          <t>Mạch Đất Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Nơi Các Vì Sao Rơi Xuống</t>
+          <t>Nơi Sao Rơi Như Mưa</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Dấu chân trên Frostlands</t>
+          <t>Dấu chân trên vùng đất băng giá</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Implementation</t>
+          <t>Chiến Dịch Lollo: Thực Thi</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Những Món Quà Từ Tuyết Mềm</t>
+          <t>Quà Tặng Tuyết Mềm</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Mạch Đất Của Vùng Băng Giá</t>
+          <t>Mạch Đất Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Intel Briefing</t>
+          <t>Báo cáo Tình báo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Startorch Dành Cho Bạn</t>
+          <t>Sao Chổi Dành Cho Bạn</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Unsigned Good Wishes</t>
+          <t>Lời Chúc Không Ký Tên</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Lộ Trình Sao Đan Xen</t>
+          <t>Những Con Đường Sao Đan Xen</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Startorch Dành Cho Bạn</t>
+          <t>Sao Chổi Dành Cho Bạn</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Unsigned Good Wishes</t>
+          <t>Lời Chúc Không Ký Tên</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Lộ Trình Sao Đan Xen</t>
+          <t>Những Con Đường Sao Đan Xen</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Echo: Nameless Explorer</t>
+          <t>Echo: Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Sonata: Trailblazing Star</t>
+          <t>Sonata: Ngôi Sao Tiên Phong</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Sonata: Chromatic Foam</t>
+          <t>Sonata: Bọt Sắc Màu</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Sonata: Sound of True Name</t>
+          <t>Sonata: Âm Thanh Của Chân Danh</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Glacier Track</t>
+          <t>Vết Tích Băng Giá</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tất cả-Terrain Tactics</t>
+          <t>Chiến Thuật Đa Địa Hình</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hợp Nhất &amp; Chỉnh Sửa Dữ Liệu</t>
+          <t>Hợp nhất &amp; Chỉnh sửa dữ liệu</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Glacier Track</t>
+          <t>Vết Tích Băng Giá</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tất cả-Terrain Tactics</t>
+          <t>Chiến Thuật Đa Địa Hình</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Hợp Nhất &amp; Chỉnh Sửa Dữ Liệu</t>
+          <t>Hợp nhất &amp; Chỉnh sửa dữ liệu</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Windlash Coleoid</t>
+          <t>Mực Gió Giật</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Frostbite Coleoid</t>
+          <t>Mực Băng Giá Coleoid</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Sabercat Prowler</t>
+          <t>Kẻ Rình Rập Mèo Đao</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Phagosite: Bipolarch</t>
+          <t>Phagosite: Song Cực Thạch</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Phagosite: Bipolarch</t>
+          <t>Phagosite: Song Cực Thạch</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Epiphany</t>
+          <t>Giác Ngộ</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Fatality</t>
+          <t>Cú Đòn Quyết Định</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Epiphany</t>
+          <t>Giác Ngộ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Perfect Harmony</t>
+          <t>Hòa Âm Hoàn Hảo</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Elegant Demeanor</t>
+          <t>Thái Độ Thanh Lịch</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Surgical Precision</t>
+          <t>Độ Chính Xác Ngoại Khoa</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Critical Hit: Vicious</t>
+          <t>Bạo Kích: Tàn Bạo</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Whiplash</t>
+          <t>Quất Mạnh</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Transcendence</t>
+          <t>Siêu Việt</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Straight A's Instinct</t>
+          <t>Bản năng xuất sắc</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Transcript</t>
+          <t>Bản sao lưu</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Bài thi hiện tại</t>
+          <t>Bài Kiểm Tra Hiện Tại</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Boss Progress</t>
+          <t>Tiến Độ Đánh Đầu Sỏ</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Exam Details</t>
+          <t>Chi tiết bài kiểm tra</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Lưu và Thoát</t>
+          <t>Lưu và thoát</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Cấp Độ GPA</t>
+          <t>CẤP ĐỘ GPA</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cấp độ GPA tạm thời</t>
+          <t>Cấp Độ GPA Tạm Thời</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ GPA</t>
+          <t>Nâng Cấp GPA</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Độ Khó Tiếp Theo</t>
+          <t>Độ khó tiếp theo</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Sửa Chữa Mechascout</t>
+          <t>Sửa Máy Tuần Tra Cơ Giới</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Giảm Độ Khó</t>
+          <t>Giảm độ khó</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Quay Lại Bài Thi</t>
+          <t>Quay lại với kỳ thi</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Độ khó bài thi</t>
+          <t>Độ khó bài kiểm tra</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Cấp Độ GPA Hiện Tại Thấp Hơn Mức Khuyến Nghị</t>
+          <t>Cấp GPA hiện tại thấp hơn mức khuyến nghị</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Repairs Complete</t>
+          <t>Hoàn tất sửa chữa</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tất Cả Mechascout Cỡ Trung Trong Bài Thi Đã Được Sửa Chữa</t>
+          <t>Tất cả Mechascout Trung đã được sửa chữa trong kỳ thi này</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tất Cả Mechascout Cỡ Nặng Trong Bài Thi Đã Được Sửa Chữa</t>
+          <t>Tất cả Mechascout hạng nặng trong kỳ thi này đã được sửa chữa</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ GPA</t>
+          <t>Nâng Cấp GPA</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Exam Details</t>
+          <t>Chi tiết bài kiểm tra</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Bắt Đầu</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Node Locked</t>
+          <t>Nút Đã Khóa</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Chọn Resonator Của Bạn</t>
+          <t>Chọn Resonator của bạn</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Trial Resonators</t>
+          <t>Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>My Resonators</t>
+          <t>Những Resonator của ta...</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Exam</t>
+          <t>Bài kiểm tra</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Chi tiết Resonator</t>
+          <t>Thông Tin Resonator</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Bắt Đầu</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Cấp Độ GPA</t>
+          <t>CẤP ĐỘ GPA</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Special Vật tư</t>
+          <t>Nguồn Cung Ứng Đặc Biệt</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Phần Thưởng Theo Hạng</t>
+          <t>Phần Thưởng Theo Cấp</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Đang Thi...</t>
+          <t>Đang Thi</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Cấp Độ GPA</t>
+          <t>CẤP ĐỘ GPA</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Exam</t>
+          <t>Bài kiểm tra</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Exam Details</t>
+          <t>Chi tiết bài kiểm tra</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Độ khó bài thi</t>
+          <t>Độ khó bài kiểm tra</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Cấp GPA Không Đủ</t>
+          <t>Cấp độ GPA không đủ</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Current Node</t>
+          <t>Nút Hiện Tại</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Exam</t>
+          <t>Bài kiểm tra</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship</t>
+          <t>Đua Cubie: Giải Vô Địch</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship</t>
+          <t>Đua Cubie: Giải Vô Địch</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Examiner 1</t>
+          <t>Giám định viên 1</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Examiner 2</t>
+          <t>Giám khảo 2</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Examiner 3</t>
+          <t>Giám khảo 3</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Examiner 4</t>
+          <t>Giám khảo 4</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Examiner 5</t>
+          <t>Giám khảo 5</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Examiner 6</t>
+          <t>Giám khảo 6</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Examiner 7</t>
+          <t>Giám khảo 7</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Examiner 8</t>
+          <t>Giám khảo 8</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Bài thi mới có sẵn</t>
+          <t>Bài kiểm tra mới đã có!</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Dùng Sigrika để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Sigrika để vượt tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Dùng Aemeath để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Aemeath để vượt Tháp Hazard từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Dùng Augusta để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Augusta để vượt từ tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Dùng Phrolova để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Phrolova để vượt Tháp Nguy Hiểm từ tầng 1 đến tầng 4 trong Tháp Thử Thách: Vùng Nguy Hiểm.</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Cartethyia để vượt từ tầng 1 đến tầng 4 của Tháp Nguy Hiểm trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Dùng Galbrena để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Nguy Hiểm</t>
+          <t>Dùng Galbrena để vượt tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Dùng Sigrika để vượt Dòng Nước Trỗi Dậy: Dòng Chảy Xiết ở Vùng Đất Than Thở</t>
+          <t>Dùng Sigrika để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Dùng Augusta hoặc Phrolova để vượt Dòng Nước Trỗi Dậy: Dòng Chảy Xiết ở Vùng Đất Than Thở</t>
+          <t>Dùng Augusta hoặc Phrolova để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia hoặc Galbrena để vượt Dòng Nước Trỗi Dậy: Dòng Chảy Xiết ở Vùng Đất Than Thở</t>
+          <t>Dùng Cartethyia hoặc Galbrena để vượt qua "Nước Trỗi Dậy: Dòng Chảy" ở Whimpering Wastes.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Dùng Aemeath hoặc Luuk Herssen để vượt Dòng Nước Trỗi Dậy: Dòng Chảy Xiết ở Vùng Đất Than Thở</t>
+          <t>Dùng Aemeath hoặc Luuk Herssen để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Hoàn thành Hiệp Ước Ổn Định với bất kỳ đội nào trong Ma Trận Tận Cùng</t>
+          <t>Hoàn thành Hiệp Ước Ổn Định với bất kỳ đội nào trong Ma Trận Trạng Thái Cuối</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Vượt "Phagosite: Bipolarch" và "TD Combo" trong Khu Huấn Luyện Tiên Phong</t>
+          <t>Hoàn thành "Phagosite: Bipolarch" và "TD Combo" tại Pioneer Training Ground.</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Vượt Bài thi 1, Bài thi 2 và Bài thi 3 của Knights of the Wild</t>
+          <t>Hoàn thành Kỳ thi Kỵ Sĩ Hoang Dã 1, 2 và 3</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Vượt Bài thi 4 và Bài thi 5 của Knights of the Wild</t>
+          <t>Hoàn thành Kỳ thi Kỵ Sĩ Hoang Dã 4 và 5</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Vượt Bài thi 6 và Bài thi 7 của Knights of the Wild</t>
+          <t>Hoàn thành Kỳ thi Kỵ Sĩ Hoang Dã 6 và 7</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Vượt "Khoảnh Khắc Giữa Các Vì Sao" ở độ khó Thường với Hạng A trở lên</t>
+          <t>Hoàn thành "Moments Captured Among the Stars" ở độ khó Thông Thường với xếp hạng A trở lên.</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Vượt "Nhảy Múa Giữa Ảo Ảnh" ở độ khó Thường với Hạng A trở lên</t>
+          <t>Hoàn thành "Nhảy Múa Giữa Ảo Giác" ở độ khó Bình Thường với xếp hạng A trở lên.</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Hoàn thành "Daisy Crown" ở độ khó Thường với xếp hạng A hoặc cao hơn</t>
+          <t>Hoàn thành "Vương Miện Cúc" ở độ khó Bình Thường với xếp hạng A trở lên.</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hoàn thành "Radiance Across Sea and Sky" ở độ khó Thường với xếp hạng A hoặc cao hơn</t>
+          <t>Hoàn thành "Radiance Across Sea and Sky" ở độ khó Thông Thường với xếp hạng A trở lên.</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Đã kích hoạt tạm thời</t>
+          <t>Kích hoạt tạm thời</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Not Activated</t>
+          <t>Chưa Kích Hoạt</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Windlash Coleoid</t>
+          <t>Mực Gió Giật</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Frostbite Coleoid</t>
+          <t>Mực Băng Giá Coleoid</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Nightmare Stirs I</t>
+          <t>Ác Mộng Thức Tỉnh I</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Nightmare Stirs II</t>
+          <t>Ác Mộng Thức Tỉnh II</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Nightmare Stirs III</t>
+          <t>Ác Mộng Thức Tỉnh III</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Nightmare Stirs IV</t>
+          <t>Ác Mộng Thức Tỉnh IV</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Nightmare Barrier I</t>
+          <t>Rào Cản Ác Mộng I</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Nightmare Barrier II</t>
+          <t>Rào Cản Ác Mộng II</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Nightmare Barrier III</t>
+          <t>Rào Cản Ác Mộng III</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Nightmare Barrier IV</t>
+          <t>Rào Cản Ác Mộng IV</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Iron Nightmare</t>
+          <t>Ác Mộng Thép</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Treatment Issue I</t>
+          <t>Vấn Đề Điều Trị I</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Treatment Issue II</t>
+          <t>Vấn Đề Điều Trị II</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Treatment Issue III</t>
+          <t>Vấn Đề Điều Trị III</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Lost Dream I</t>
+          <t>Giấc Mơ Lạc Lối I</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Lost Dream II</t>
+          <t>Giấc Mơ Lạc Lối II</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trong Mộng I</t>
+          <t>Giấc Mơ Trong Giấc Mơ I</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trong Mộng II</t>
+          <t>Giấc Mơ Trong Giấc Mơ II</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trong Mộng III</t>
+          <t>Giấc Mộng Trong Giấc Mộng III</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trong Mộng IV</t>
+          <t>Giấc Mộng Trong Giấc Mộng IV</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trong Mộng V</t>
+          <t>Giấc Mộng Trong Giấc Mộng V</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Dream Inflation</t>
+          <t>Giấc Mơ Bành Trướng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khởi đầu chậm</t>
+          <t>Khởi Đầu Chậm</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Nightmare Begins</t>
+          <t>Ác Mộng Bắt Đầu</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Hot Barrel</t>
+          <t>Nòng Súng Nóng</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Speed Loader</t>
+          <t>Nạp Nhanh</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Full Salvo</t>
+          <t>Toàn Lực Phóng</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Tăng gấp đôi chi phí để làm mới Metaphor, Token hoặc vật phẩm trong cửa hàng có sẵn</t>
+          <t>Tăng gấp đôi chi phí làm mới Thể Loại, Thẻ hoặc vật phẩm trong Cửa Hàng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Enemy Enhancement</t>
+          <t>Tăng cường kẻ địch</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Resonator Debuff</t>
+          <t>Hiệu Ứng Bất Lợi Cho Resonator</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Cơ chế Đặc biệt</t>
+          <t>Cơ Chế Đặc Biệt</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Unactivated</t>
+          <t>Chưa kích hoạt</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Chọn Resonator chính</t>
+          <t>Chọn Resonator Chính</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Khởi đầu giấc mơ I</t>
+          <t>Khởi Đầu Giấc Mơ I</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Dream Đặt lại I</t>
+          <t>Thiết Lập Lại Giấc Mơ I</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Kích ATK</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>DEF Boost</t>
+          <t>TĂNG PHÒNG NGỤ</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Dream Flicker</t>
+          <t>Lấp Lánh Giấc Mơ</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Dreammaker I</t>
+          <t>Người Dệt Giấc Mơ I</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Cửa hàng Refresh</t>
+          <t>Làm Mới Cửa Hàng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Deconstructive Aid</t>
+          <t>Hỗ Trợ Phá Hủy</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>HP Boost</t>
+          <t>Tăng HP</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>DMG Boost</t>
+          <t>Tăng Cường Sát Thương</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Absorber</t>
+          <t>Hấp thụ</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Dreamscape Dancer</t>
+          <t>Vũ Công Cảnh Mộng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Symphony Crescendo</t>
+          <t>Khúc Giao Hưởng Bùng Nổ</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Dream Đặt lại II</t>
+          <t>Đặt Lại Giấc Mơ II</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Dreammaker II</t>
+          <t>Người Dệt Giấc Mơ II</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khởi đầu giấc mơ II</t>
+          <t>Khởi Đầu Giấc Mơ II</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Namipon's Aid II</t>
+          <t>Hỗ Trợ Của Namipon II</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Silver Lining</t>
+          <t>Lằn Sáng Bạc</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Reverie Gift</t>
+          <t>Món Quà Ảo Mộng</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Reverie Dancer</t>
+          <t>Vũ Điệu Ảo Mộng</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Dreamkeeper</t>
+          <t>Người Giữ Giấc Mơ</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dreamscape Resonance</t>
+          <t>Cộng Hưởng Mộng Ảo</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Dreamscape Blade</t>
+          <t>Kiếm Cảnh Mộng</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Symphony Climax</t>
+          <t>Đỉnh Cao Giao Hưởng</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>DEF Surge</t>
+          <t>Phòng Ngự Bùng Nổ</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>ATK Surge</t>
+          <t>Bùng Nổ ATK</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>HP Surge</t>
+          <t>Bùng Nổ HP</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>DMG Surge</t>
+          <t>Dâng Sát Thương</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Hoàn thành Chromatic Fantasy I để mở khóa</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu I để mở khóa</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Hoàn thành Chromatic Fantasy II để mở khóa</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu II để mở khóa</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Hoàn thành Chromatic Fantasy III để mở khóa</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu III để mở khóa</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Hoàn thành Chromatic Fantasy IV để mở khóa</t>
+          <t>Hoàn thành Bản Giao Hưởng Sắc Màu IV để mở khóa</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Hoàn thành với tỷ lệ phần thưởng 200% để mở khóa</t>
+          <t>Hoàn thành với Tỷ Lệ Phần Thưởng 200% để mở khóa</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hoàn thành với tỷ lệ phần thưởng 300% để mở khóa</t>
+          <t>Hoàn thành với Tỷ Lệ Phần Thưởng 300% để mở khóa</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Vào Chromatic Fantasy II và các màn sau để mở khóa</t>
+          <t>Hoàn thành Giấc Mơ Sắc Màu II và các màn sau để mở khóa</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Vào Chromatic Fantasy III và các màn sau để mở khóa</t>
+          <t>Hoàn thành Giấc Mơ Sắc Màu III và các màn sau để mở khóa</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Vào Chromatic Fantasy IV và các màn sau để mở khóa</t>
+          <t>Hoàn thành Giấc Mơ Sắc Màu IV và các màn sau để mở khóa</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Bề mặt ảo giác</t>
+          <t>Bề Mặt Ảo Ảnh</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Độ Sâu Ảo Giác</t>
+          <t>Ảo Ảnh Vực Sâu</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Crownless một lần</t>
+          <t>Hoàn thành thử thách với Illusive Echo: Crownless once</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: False Sovereign một lần</t>
+          <t>Hoàn thành thử thách Illusive Echo: False Sovereign một lần</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Sigillum một lần</t>
+          <t>Hoàn thành thử thách Illusive Echo: Sigillum một lần</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Inferno Rider một lần</t>
+          <t>Hoàn thành thử thách Illusive Echo: Inferno Rider once</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Dreamless một lần</t>
+          <t>Hoàn thành thử thách Illusive Echo: Dreamless once</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Bell-Borne Geochelone một lần</t>
+          <t>Hoàn thành thử thách với Illusive Echo: Bell-Borne Geochelone once</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Illusive Echo: Thundering Mephis một lần</t>
+          <t>Hoàn thành thử thách Illusive Echo: Thundering Mephis once</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả các nút Tiến Hóa Tư Tưởng</t>
+          <t>Mở khóa tất cả Nút Tiến Hóa Ý Thức.</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy II</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu II</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy III</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu III</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy IV</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu IV</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành Chromatic Fantasy IV một lần với Tỉ lệ Phần thưởng 300%</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu IV một lần với Tỷ Lệ Phần Thưởng 300%</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Kích hoạt Illusification thứ tư của bất kỳ Illusive Echo nào</t>
+          <t>Kích hoạt Hóa Ảo Thứ Tư của bất kỳ Ảo Ảnh Echo nào</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy I</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu I</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy II</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu II</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy III</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu III</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Clear Chromatic Fantasy IV</t>
+          <t>Hoàn thành Ảo Ảnh Sắc Màu IV</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Không thể tìm thấy Cube theo thứ tự chỉ định</t>
+          <t>Không tìm thấy Khối Lập Phương theo cấp đã chỉ định</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Unknown Sender</t>
+          <t>Người gửi bí ẩn</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Preliminary Showmatch</t>
+          <t>Trận Đấu Thử Sơ Bộ</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Eliminator A</t>
+          <t>Diệt Trừ Giả A</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Eliminator B</t>
+          <t>Diệt Trừ Giả B</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Upper Eliminator</t>
+          <t>Thanh Toán Thượng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Lower Eliminator</t>
+          <t>Giảm số lượng Loại Trừ</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Playoff</t>
+          <t>Vòng đấu loại trực tiếp</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Eliminator Showmatch</t>
+          <t>Trận Đấu Diệt Trừ</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>B - Hạng 1</t>
+          <t>B - Lần đầu tiên</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>B - Hạng 2</t>
+          <t>B - Lần thứ hai</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>C - Hạng 1</t>
+          <t>C - Thứ nhất</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>C - Hạng 2</t>
+          <t>C - Thứ hai</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Vòng 1</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Vòng 2</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Thượng</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Giảm xuống</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Playoff</t>
+          <t>Vòng đấu loại trực tiếp</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hạng 1</t>
+          <t>Lần 1</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hạng 2</t>
+          <t>Lượt thứ 2</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Hạng 1</t>
+          <t>Lần 1</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Hạng 2</t>
+          <t>Lượt thứ 2</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Hạng 1</t>
+          <t>Lần 1</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Hạng 2</t>
+          <t>Lượt thứ 2</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Vòng 1</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Vòng 2</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Round 3</t>
+          <t>Vòng 3</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Round 4</t>
+          <t>Vòng 4</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Round 5</t>
+          <t>Vòng 5</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Upper (6→3)</t>
+          <t>Thượng (6→3)</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Lower (6→3)</t>
+          <t>Giảm xuống (6→3)</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Playoff (6→3)</t>
+          <t>Vòng đấu loại trực tiếp (6→3)</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Thượng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Giảm xuống</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Playoff</t>
+          <t>Vòng đấu loại trực tiếp</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Showmatch</t>
+          <t>Trận đấu trình diễn</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Tiến vào Vòng Loại Trực Tiếp</t>
+          <t>Thăng cấp lên Eliminator</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tiến vào Chung Kết</t>
+          <t>Tiến vào vòng chung kết</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Preliminary</t>
+          <t>Vòng Sơ Loại</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Eliminator</t>
+          <t>Diệt Trừ Giả</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Thruster</t>
+          <t>Động Cơ Phản Lực</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>Chướng ngại</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Spatial Rift</t>
+          <t>Vết Rách Không Gian</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Abbowser Cube</t>
+          <t>Khối Abbowser</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Lynae Cube</t>
+          <t>Khối Lynae</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Mornye Cube</t>
+          <t>Khối Mornye</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Aemeath Cube</t>
+          <t>Khối Lập Phương Aemeath</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Luuk Herssen Cube</t>
+          <t>Khối Lập Phương Luuk Herssen</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Sigrika Cube</t>
+          <t>Khối Sigrika</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hiyuki Cube</t>
+          <t>Khối Lập Phương Hiyuki</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Denia Cube</t>
+          <t>Khối Denia</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Chisa Cube</t>
+          <t>Khối Chisa</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Phrolova Cube</t>
+          <t>Khối Phrolova</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Augusta Cube</t>
+          <t>Khối lập phương Augusta</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Iuno Cube</t>
+          <t>Khối Iuno</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Abbowser Cube</t>
+          <t>Khối Abbowser</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Precision Computing</t>
+          <t>Tính Toán Chính Xác</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Digital Ghost</t>
+          <t>Hồn Ma Số</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Guiding White Bird</t>
+          <t>Chim Trắng Dẫn Đường</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Đôi Điều Tốt Lành</t>
+          <t>Đôi khi điều tốt đẹp lại đến theo cặp</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Infinite Vision</t>
+          <t>Thị Giác Vô Tận</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Elegant Intrigue</t>
+          <t>Âm Mưu Thanh Lịch</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ephor's Scepter</t>
+          <t>Quyền Trượng Ephor</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Điểm Neo Định Mệnh</t>
+          <t>Mỏ Neo Định Mệnh</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Thruster</t>
+          <t>Động Cơ Phản Lực</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>Chướng ngại</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Spatial Rift</t>
+          <t>Vết Rách Không Gian</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Mechanisms</t>
+          <t>Cơ Cấu</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 1 trận trên trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả của 1 trận đấu trên trang sự kiện</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 9 trận trên trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 9 trận đấu trên trang sự kiện</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nhận 5.000 điểm Uy Tín qua Ủng hộ</t>
+          <t>Thu thập 5.000 Điểm Phổ Biến qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Nhận 10.000 điểm Uy Tín qua Ủng hộ</t>
+          <t>Nhận 10.000 Điểm Phổ Biến qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Nhận 20.000 điểm Uy tín qua Hỗ trợ</t>
+          <t>Đạt 20.000 điểm Nổi tiếng qua Hỗ trợ</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhận 30.000 điểm Uy tín qua Hỗ trợ</t>
+          <t>Thu thập 30.000 điểm Nổi Tiếng thông qua Hỗ Trợ.</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Nhận 50.000 điểm Uy tín qua Hỗ trợ</t>
+          <t>Đạt 50.000 điểm Uy Danh qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Nhận 100.000 điểm Uy tín qua Hỗ trợ</t>
+          <t>Đạt 100.000 điểm Nổi Tiếng thông qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Nhận 250.000 điểm Uy tín qua Hỗ trợ</t>
+          <t>Nhận 250.000 Điểm Nổi Tiếng qua Hỗ Trợ.</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đang trong Giai đoạn Hỗ trợ</t>
+          <t>Giai đoạn Hỗ trợ bắt đầu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Leave Confirmation</t>
+          <t>Xác nhận rời đi</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Xuất sắc! Bài kiểm tra Thành thạo Chiến đấu!</t>
+          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Chiến Đấu!</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Phần thưởng Giới hạn Thời gian</t>
+          <t>Các Phần Thưởng Giới Hạn</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Kỷ lục tốt nhất</t>
+          <t>Kỷ Lục Tốt Nhất</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Test Details</t>
+          <t>Chi Tiết Kiểm Tra</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Không có Điểm</t>
+          <t>Không Điểm Số</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Test Objectives</t>
+          <t>Mục Tiêu Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Preliminary Test</t>
+          <t>Bài Kiểm Tra Sơ Bộ</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Sử dụng cơ chế của trung tâm kiểm tra để đánh bại các Giám khảo Cộng tác và nhận buff trạng thái</t>
+          <t>Sử dụng cơ chế của trung tâm thử nghiệm để đánh bại các Giám Khảo Cộng Tác và nhận được buff trạng thái</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Final Test</t>
+          <t>Bài Kiểm Tra Cuối Cùng</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Assessor Traits</t>
+          <t>Đặc Tính Người Đánh Giá</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Test Center Mechanics</t>
+          <t>Cơ chế kiểm tra trung tâm</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Được đề xuất</t>
+          <t>Đề xuất</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Bắt đầu Kiểm tra</t>
+          <t>Bắt Đầu Kiểm Tra</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu kiểm tra với đội hình trống</t>
+          <t>Không thể bắt đầu thử nghiệm với đội hình trống</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Assessor List</t>
+          <t>Danh Sách Người Đánh Giá</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Buffss</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Preliminary Test - Associate Assessors</t>
+          <t>Bài Kiểm Tra Sơ Bộ - Giám Khảo Cộng Tác</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Tương tác với Chìa khóa Tàn tích để bắt đầu kiểm tra</t>
+          <t>Tương tác với Chìa Khóa Tàn Dư để bắt đầu bài kiểm tra</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tầng hiện tại x</t>
+          <t>Số Lượng Hiện Tại x</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Final Test - Chief Assessor</t>
+          <t>Bài Kiểm Tra Cuối - Giám Khảo Trưởng</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Objective Not Met</t>
+          <t>Chưa đạt yêu cầu nhiệm vụ</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Quit Test</t>
+          <t>Thoát Kiểm Tra</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Retake Test</t>
+          <t>Thử Lại Bài Kiểm Tra</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Điều chỉnh Lineup</t>
+          <t>Điều chỉnh đội hình</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Test Complete</t>
+          <t>Hoàn tất kiểm tra</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Chief Assessor Defeats:</t>
+          <t>Số lần đánh bại Người Giám Định Trưởng:</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>New Record</t>
+          <t>Kỷ Lục Mới</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Retake Test</t>
+          <t>Thử Lại Bài Kiểm Tra</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Bắt đầu lại từ "Giám khảo trưởng Cuối cùng"</t>
+          <t>Bắt đầu lại từ "Giám Khảo Trưởng Vòng Chung Kết"</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Xác nhận Điểm</t>
+          <t>Xác nhận Điểm số</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Quit Confirmation</t>
+          <t>Xác Nhận Thoát</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Quit Test</t>
+          <t>Thoát Kiểm Tra</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Retake Test</t>
+          <t>Thử Lại Bài Kiểm Tra</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>False Sovereign</t>
+          <t>Chúa tể giả hiệu</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Penetration Shard</t>
+          <t>Mảnh Xuyên Phá</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Off-Tune Core</t>
+          <t>Lõi Lệch Tần</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tune Strain Core</t>
+          <t>Lõi Tune Strain</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Tune Rupture Core</t>
+          <t>Điều Chỉnh Lõi Vết Nứt.</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Echo Core</t>
+          <t>Lõi Tiếng Vọng</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Phát hiện lỗi dữ liệu</t>
+          <t>Phát hiện lỗi dữ liệu.</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Không thể tham gia sự kiện này trong Chế độ Hợp tác</t>
+          <t>Không thể tham gia sự kiện này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Taoyuan Vale</t>
+          <t>Thung Lũng Đào Nguyên</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Honami City</t>
+          <t>Thành Phố Honami</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
